--- a/artfynd/A 37061-2021 artfynd.xlsx
+++ b/artfynd/A 37061-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37061-2021 artfynd.xlsx
+++ b/artfynd/A 37061-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97365141</v>
+        <v>97365124</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531486.3626455581</v>
+        <v>531544</v>
       </c>
       <c r="R2" t="n">
-        <v>6967410.475494117</v>
+        <v>6967491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97365146</v>
+        <v>97365086</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531538.8850596678</v>
+        <v>531479</v>
       </c>
       <c r="R3" t="n">
-        <v>6967373.508883998</v>
+        <v>6967399</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97365132</v>
+        <v>97365088</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531524.5687102439</v>
+        <v>531571</v>
       </c>
       <c r="R4" t="n">
-        <v>6967387.080287506</v>
+        <v>6967387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,21 +955,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1013,6 +968,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1033,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97365086</v>
+        <v>97365136</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531478.2317505826</v>
+        <v>531544</v>
       </c>
       <c r="R5" t="n">
-        <v>6967399.430322711</v>
+        <v>6967491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,19 +1061,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97365158</v>
+        <v>97365142</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531562.7665299698</v>
+        <v>531530</v>
       </c>
       <c r="R6" t="n">
-        <v>6967364.599207835</v>
+        <v>6967502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,21 +1167,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1250,6 +1180,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97365099</v>
+        <v>97365146</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531552.6208912577</v>
+        <v>531539</v>
       </c>
       <c r="R7" t="n">
-        <v>6967372.727044738</v>
+        <v>6967373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,21 +1273,11 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1366,6 +1286,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1379,6 +1304,723 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97365154</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>531428</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967433</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97365141</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>531486</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967411</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97365099</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>531553</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967373</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97365131</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>531427</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6967431</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97365132</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>531525</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6967387</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>97365133</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>531458</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6967408</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97365158</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kullan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>531563</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6967365</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
